--- a/данные/тест_реал/заполненные/Учителя - Пятница.xlsx
+++ b/данные/тест_реал/заполненные/Учителя - Пятница.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuMon1x\AMSUR\данные\тест_реал\заполненные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FCF366-6E36-4ACC-8520-D78FA3F6B036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBBC37F-6169-42C5-9A12-7464D9702CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="85">
   <si>
     <t>Преподователи</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>над.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    </t>
   </si>
 </sst>
 </file>
@@ -308,7 +311,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -638,20 +642,20 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -698,6 +702,9 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="G3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -941,7 +948,7 @@
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
@@ -1231,12 +1238,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -1256,7 +1263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -1273,7 +1280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -1293,7 +1300,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -1316,7 +1323,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -1330,7 +1337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1347,7 +1354,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1367,7 +1374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -1393,17 +1400,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -1426,7 +1433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -1449,7 +1456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1457,7 +1464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -1474,32 +1481,32 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>77</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" s="1" t="s">
         <v>25</v>
       </c>
     </row>
